--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל מויאל - חי באנשים</v>
+        <v>יוני מאמוש - חרפה לאמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410482&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410492&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל מויאל - חי באנשים</v>
+        <v>יוני מאמוש - חרפה לאמת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
+        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410481&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410491&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
+        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל וייס - העם הנבחר</v>
+        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410480&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410490&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל וייס - העם הנבחר</v>
+        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דודי בר דוד - כל ההכי טובים</v>
+        <v>הנרי תנך - שרשרת הבטחות</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410479&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410489&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דודי בר דוד - כל ההכי טובים</v>
+        <v>הנרי תנך - שרשרת הבטחות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אייל בוגט - חיבוק פרידה</v>
+        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410478&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410488&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,50 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אייל בוגט - חיבוק פרידה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אופק לוי - שלוש שאלות</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410477&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אופק לוי - שלוש שאלות</v>
+        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני מאמוש - חרפה לאמת</v>
+        <v>ספיר עמר - שתשוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410492&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410501&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני מאמוש - חרפה לאמת</v>
+        <v>ספיר עמר - שתשוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+        <v>הראל בשארי - אומרי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410491&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410500&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-16</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+        <v>הראל בשארי - אומרי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+        <v>שליו מרציאנו - אבא גיבור</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410490&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410499&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-16</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+        <v>שליו מרציאנו - אבא גיבור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הנרי תנך - שרשרת הבטחות</v>
+        <v>שי מנדל &amp; הראל סבג - מצטער</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410489&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410498&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-16</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>הנרי תנך - שרשרת הבטחות</v>
+        <v>שי מנדל &amp; הראל סבג - מצטער</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
+        <v>רגב הוד - מלכודת דבש 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410488&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410497&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-16</v>
@@ -621,12 +621,164 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
+        <v>רגב הוד - מלכודת דבש 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ספיר עמר - מתגעגעת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410496&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ספיר עמר - מתגעגעת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מיכל גרינגליק - לוח זכרונות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410495&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מיכל גרינגליק - לוח זכרונות</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410494&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ליאור נרקיס - את משגעת אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410493&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ליאור נרקיס - את משגעת אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר עמר - שתשוב</v>
+        <v>עמית הלוי - מחכה שהוא ישוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410501&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410526&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר עמר - שתשוב</v>
+        <v>עמית הלוי - מחכה שהוא ישוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הראל בשארי - אומרי</v>
+        <v>קורל - שגעון חולף</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410500&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410525&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הראל בשארי - אומרי</v>
+        <v>קורל - שגעון חולף</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שליו מרציאנו - אבא גיבור</v>
+        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410499&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410524&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שליו מרציאנו - אבא גיבור</v>
+        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שי מנדל &amp; הראל סבג - מצטער</v>
+        <v>דודי בוזגלו - אהובי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410498&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410523&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שי מנדל &amp; הראל סבג - מצטער</v>
+        <v>דודי בוזגלו - אהובי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רגב הוד - מלכודת דבש 2026</v>
+        <v>גל סינואני - מי יתן מציון</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410497&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410522&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רגב הוד - מלכודת דבש 2026</v>
+        <v>גל סינואני - מי יתן מציון</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ספיר עמר - מתגעגעת</v>
+        <v>גל אהרוני - שמע ישראל</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410496&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410521&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ספיר עמר - מתגעגעת</v>
+        <v>גל אהרוני - שמע ישראל</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מיכל גרינגליק - לוח זכרונות</v>
+        <v>גבריאל זאודו - בואי הביתה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410495&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410520&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מיכל גרינגליק - לוח זכרונות</v>
+        <v>גבריאל זאודו - בואי הביתה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
+        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410494&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410519&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,50 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ליאור נרקיס - את משגעת אותי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410493&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ליאור נרקיס - את משגעת אותי</v>
+        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית הלוי - מחכה שהוא ישוב</v>
+        <v>ינון שניר - חיה על מזוודות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410526&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410538&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית הלוי - מחכה שהוא ישוב</v>
+        <v>ינון שניר - חיה על מזוודות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קורל - שגעון חולף</v>
+        <v>יוסי שטרית - הסוד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410525&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410537&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קורל - שגעון חולף</v>
+        <v>יוסי שטרית - הסוד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
+        <v>דניאל אזולאי - האושר איתך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410524&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410536&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
+        <v>דניאל אזולאי - האושר איתך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דודי בוזגלו - אהובי</v>
+        <v>אמיר שדה - שמות</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410523&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410535&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דודי בוזגלו - אהובי</v>
+        <v>אמיר שדה - שמות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>גל סינואני - מי יתן מציון</v>
+        <v>אריק סיני - פרח</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410522&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410534&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>גל סינואני - מי יתן מציון</v>
+        <v>אריק סיני - פרח</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>גל אהרוני - שמע ישראל</v>
+        <v>קלימה - תמיד להיות בשמחה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410521&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410532&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>גל אהרוני - שמע ישראל</v>
+        <v>קלימה - תמיד להיות בשמחה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>גבריאל זאודו - בואי הביתה</v>
+        <v>קלימה - יש לי הכל</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410520&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410531&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>גבריאל זאודו - בואי הביתה</v>
+        <v>קלימה - יש לי הכל</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
+        <v>קלימה - יום ועוד יום</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410519&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410530&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,12 +735,126 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
+        <v>קלימה - יום ועוד יום</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>קלימה - הכל לטובה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410529&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>קלימה - הכל לטובה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>קלימה - הכל בידיים שלו</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410528&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>קלימה - הכל בידיים שלו</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>קלימה - אולי הפעם</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410527&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>קלימה - אולי הפעם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ינון שניר - חיה על מזוודות</v>
+        <v>צדוק - באתי מתימן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410538&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410544&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ינון שניר - חיה על מזוודות</v>
+        <v>צדוק - באתי מתימן</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוסי שטרית - הסוד</v>
+        <v>עברי לידר - מכתב מהעורף</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410537&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410543&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוסי שטרית - הסוד</v>
+        <v>עברי לידר - מכתב מהעורף</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל אזולאי - האושר איתך</v>
+        <v>נועם ראש - איטליה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410536&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410542&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל אזולאי - האושר איתך</v>
+        <v>נועם ראש - איטליה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אמיר שדה - שמות</v>
+        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410535&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410541&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אמיר שדה - שמות</v>
+        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אריק סיני - פרח</v>
+        <v>ליאן סויסה - הלילות - קורת חיים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410534&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410540&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-19</v>
@@ -621,240 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אריק סיני - פרח</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>קלימה - תמיד להיות בשמחה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410532&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>קלימה - תמיד להיות בשמחה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>קלימה - יש לי הכל</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410531&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>קלימה - יש לי הכל</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>קלימה - יום ועוד יום</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410530&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>קלימה - יום ועוד יום</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>קלימה - הכל לטובה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410529&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>קלימה - הכל לטובה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>קלימה - הכל בידיים שלו</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410528&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>קלימה - הכל בידיים שלו</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>קלימה - אולי הפעם</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410527&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>קלימה - אולי הפעם</v>
+        <v>ליאן סויסה - הלילות - קורת חיים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צדוק - באתי מתימן</v>
+        <v>בנצ'ו - רוח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410544&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410553&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צדוק - באתי מתימן</v>
+        <v>בנצ'ו - רוח</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עברי לידר - מכתב מהעורף</v>
+        <v>שיראל חדד - רק רוצה הביתה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410543&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410552&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עברי לידר - מכתב מהעורף</v>
+        <v>שיראל חדד - רק רוצה הביתה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם ראש - איטליה</v>
+        <v>רן אמור - נפלו כאן גיבורים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410542&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410551&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם ראש - איטליה</v>
+        <v>רן אמור - נפלו כאן גיבורים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
+        <v>הראל סקעת - נקום</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410541&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410549&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
+        <v>הראל סקעת - נקום</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאן סויסה - הלילות - קורת חיים</v>
+        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410540&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410548&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,126 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאן סויסה - הלילות - קורת חיים</v>
+        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אסף בר נתן - כוכבים לא נופלים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410547&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אסף בר נתן - כוכבים לא נופלים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410546&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אדיר גץ - שובר לבבות מקצועי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410545&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אדיר גץ - שובר לבבות מקצועי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>